--- a/Top 7 broker List with its Turnover 2022-12-06.xlsx
+++ b/Top 7 broker List with its Turnover 2022-12-06.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="267">
   <si>
     <t>Date: 2022-12-06</t>
   </si>
@@ -71,15 +71,15 @@
     <t>Shree Krishna Securities Limited</t>
   </si>
   <si>
+    <t>Dakshinkali Investment Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Dakshinkali Investment Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
@@ -92,76 +92,76 @@
     <t>28</t>
   </si>
   <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
     <t>38</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>151,790,043.3</t>
-  </si>
-  <si>
-    <t>107,562,433.08</t>
-  </si>
-  <si>
-    <t>106,965,645.75</t>
-  </si>
-  <si>
-    <t>88,066,633.8</t>
-  </si>
-  <si>
-    <t>70,842,017.44</t>
-  </si>
-  <si>
-    <t>63,479,283.2</t>
-  </si>
-  <si>
-    <t>60,320,644.68</t>
-  </si>
-  <si>
-    <t>79,477,607.65</t>
-  </si>
-  <si>
-    <t>36,943,844.29</t>
-  </si>
-  <si>
-    <t>46,846,918.4</t>
-  </si>
-  <si>
-    <t>23,701,602.4</t>
-  </si>
-  <si>
-    <t>22,374,893.04</t>
-  </si>
-  <si>
-    <t>34,067,005.9</t>
-  </si>
-  <si>
-    <t>39,069,896.4</t>
-  </si>
-  <si>
-    <t>72,312,435.65</t>
-  </si>
-  <si>
-    <t>70,618,588.79</t>
-  </si>
-  <si>
-    <t>60,118,727.35</t>
-  </si>
-  <si>
-    <t>64,365,031.4</t>
-  </si>
-  <si>
-    <t>48,467,124.4</t>
-  </si>
-  <si>
-    <t>29,412,277.3</t>
-  </si>
-  <si>
-    <t>21,250,748.28</t>
+    <t>150,896,735.39</t>
+  </si>
+  <si>
+    <t>104,534,743.58</t>
+  </si>
+  <si>
+    <t>98,281,028.75</t>
+  </si>
+  <si>
+    <t>89,148,791.4</t>
+  </si>
+  <si>
+    <t>66,348,491.18</t>
+  </si>
+  <si>
+    <t>65,028,299.9</t>
+  </si>
+  <si>
+    <t>64,505,209.84</t>
+  </si>
+  <si>
+    <t>76,492,555.84</t>
+  </si>
+  <si>
+    <t>32,294,688.19</t>
+  </si>
+  <si>
+    <t>42,968,938.9</t>
+  </si>
+  <si>
+    <t>23,998,778.5</t>
+  </si>
+  <si>
+    <t>44,033,387.7</t>
+  </si>
+  <si>
+    <t>34,331,272.0</t>
+  </si>
+  <si>
+    <t>22,903,995.64</t>
+  </si>
+  <si>
+    <t>74,404,179.55</t>
+  </si>
+  <si>
+    <t>72,240,055.39</t>
+  </si>
+  <si>
+    <t>55,312,089.85</t>
+  </si>
+  <si>
+    <t>65,150,012.9</t>
+  </si>
+  <si>
+    <t>22,315,103.48</t>
+  </si>
+  <si>
+    <t>30,697,027.9</t>
+  </si>
+  <si>
+    <t>41,601,214.2</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,91 +182,100 @@
     <t>NABIL</t>
   </si>
   <si>
-    <t>19,041,378.3</t>
+    <t>12,947,915.4</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>4,535,829.9</t>
+  </si>
+  <si>
+    <t>KMCDB</t>
+  </si>
+  <si>
+    <t>4,396,390.4</t>
+  </si>
+  <si>
+    <t>DDBL</t>
+  </si>
+  <si>
+    <t>3,451,010.0</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>3,128,891.1</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>3,532,184.3</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>3,027,840.0</t>
   </si>
   <si>
     <t>HDL</t>
   </si>
   <si>
-    <t>5,262,991.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>4,489,201.9</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>3,533,840.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>3,238,604.3</t>
-  </si>
-  <si>
-    <t>6,246,238.0</t>
-  </si>
-  <si>
-    <t>3,771,377.5</t>
+    <t>2,314,857.5</t>
+  </si>
+  <si>
+    <t>RSDC</t>
+  </si>
+  <si>
+    <t>1,815,640.0</t>
+  </si>
+  <si>
+    <t>1,767,826.5</t>
+  </si>
+  <si>
+    <t>4,607,357.4</t>
+  </si>
+  <si>
+    <t>4,411,536.0</t>
+  </si>
+  <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>3,452,288.0</t>
+  </si>
+  <si>
+    <t>RMDC</t>
+  </si>
+  <si>
+    <t>2,259,211.0</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>1,944,038.0</t>
+  </si>
+  <si>
+    <t>NCCB</t>
+  </si>
+  <si>
+    <t>3,511,612.9</t>
+  </si>
+  <si>
+    <t>MKJC</t>
+  </si>
+  <si>
+    <t>2,317,880.0</t>
   </si>
   <si>
     <t>NLIC</t>
   </si>
   <si>
-    <t>3,304,510.0</t>
-  </si>
-  <si>
-    <t>1,767,826.5</t>
-  </si>
-  <si>
-    <t>RSDC</t>
-  </si>
-  <si>
-    <t>1,761,940.0</t>
-  </si>
-  <si>
-    <t>5,344,278.0</t>
-  </si>
-  <si>
-    <t>4,117,757.4</t>
-  </si>
-  <si>
-    <t>LICN</t>
-  </si>
-  <si>
-    <t>3,352,748.0</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>3,240,895.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>2,074,259.6</t>
-  </si>
-  <si>
-    <t>NCCB</t>
-  </si>
-  <si>
-    <t>3,054,575.9</t>
-  </si>
-  <si>
-    <t>MKJC</t>
-  </si>
-  <si>
-    <t>2,353,700.0</t>
-  </si>
-  <si>
-    <t>1,999,096.1</t>
+    <t>2,068,648.1</t>
   </si>
   <si>
     <t>ADBL</t>
@@ -275,58 +284,25 @@
     <t>1,560,000.0</t>
   </si>
   <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>1,425,369.2</t>
-  </si>
-  <si>
-    <t>3,046,636.0</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>1,859,182.4</t>
-  </si>
-  <si>
-    <t>1,857,723.0</t>
-  </si>
-  <si>
-    <t>1,778,808.0</t>
-  </si>
-  <si>
-    <t>1,131,700.0</t>
-  </si>
-  <si>
-    <t>4,181,276.1</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>2,249,728.0</t>
-  </si>
-  <si>
-    <t>2,095,697.6</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>1,963,359.8</t>
-  </si>
-  <si>
-    <t>1,817,690.0</t>
+    <t>1,313,031.0</t>
   </si>
   <si>
     <t>NICA</t>
   </si>
   <si>
-    <t>7,867,691.0</t>
-  </si>
-  <si>
-    <t>4,450,882.2</t>
+    <t>7,242,191.0</t>
+  </si>
+  <si>
+    <t>4,523,682.2</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>3,231,090.0</t>
+  </si>
+  <si>
+    <t>2,829,762.8</t>
   </si>
   <si>
     <t>HDHPC</t>
@@ -335,160 +311,181 @@
     <t>2,794,840.0</t>
   </si>
   <si>
-    <t>2,587,212.79</t>
-  </si>
-  <si>
-    <t>1,529,391.2</t>
+    <t>2,699,491.6</t>
+  </si>
+  <si>
+    <t>2,234,392.0</t>
+  </si>
+  <si>
+    <t>2,208,873.79</t>
+  </si>
+  <si>
+    <t>2,050,260.0</t>
+  </si>
+  <si>
+    <t>1,596,850.0</t>
+  </si>
+  <si>
+    <t>3,540,109.0</t>
+  </si>
+  <si>
+    <t>2,120,828.0</t>
+  </si>
+  <si>
+    <t>1,413,562.4</t>
+  </si>
+  <si>
+    <t>1,340,963.0</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>723,432.8</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>14,985,992.6</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>7,524,000.0</t>
+    <t>15,224,519.6</t>
+  </si>
+  <si>
+    <t>7,495,547.1</t>
+  </si>
+  <si>
+    <t>4,407,022.4</t>
+  </si>
+  <si>
+    <t>3,846,109.1</t>
+  </si>
+  <si>
+    <t>3,665,603.4</t>
+  </si>
+  <si>
+    <t>13,680,805.0</t>
+  </si>
+  <si>
+    <t>12,290,875.2</t>
+  </si>
+  <si>
+    <t>6,155,210.0</t>
+  </si>
+  <si>
+    <t>3,066,172.0</t>
+  </si>
+  <si>
+    <t>3,043,940.0</t>
+  </si>
+  <si>
+    <t>5,753,555.6</t>
+  </si>
+  <si>
+    <t>OHL</t>
+  </si>
+  <si>
+    <t>4,354,191.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>3,558,980.8</t>
+  </si>
+  <si>
+    <t>MLBL</t>
+  </si>
+  <si>
+    <t>2,820,182.6</t>
+  </si>
+  <si>
+    <t>2,322,894.0</t>
+  </si>
+  <si>
+    <t>45,363,232.0</t>
+  </si>
+  <si>
+    <t>MEGA</t>
+  </si>
+  <si>
+    <t>6,919,197.6</t>
+  </si>
+  <si>
+    <t>2,728,556.0</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>1,846,544.8</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>1,645,087.4</t>
+  </si>
+  <si>
+    <t>9,473,970.19</t>
+  </si>
+  <si>
+    <t>1,602,060.0</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>1,240,282.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>585,206.3</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>561,065.0</t>
+  </si>
+  <si>
+    <t>4,874,345.59</t>
+  </si>
+  <si>
+    <t>2,147,362.7</t>
+  </si>
+  <si>
+    <t>1,324,114.6</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>1,309,761.5</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>1,169,670.0</t>
+  </si>
+  <si>
+    <t>6,512,406.0</t>
+  </si>
+  <si>
+    <t>4,455,622.5</t>
+  </si>
+  <si>
+    <t>3,430,214.7</t>
+  </si>
+  <si>
+    <t>3,160,048.0</t>
   </si>
   <si>
     <t>NESDO</t>
   </si>
   <si>
-    <t>6,394,320.0</t>
-  </si>
-  <si>
-    <t>3,709,581.1</t>
-  </si>
-  <si>
-    <t>3,385,993.4</t>
-  </si>
-  <si>
-    <t>16,316,079.2</t>
-  </si>
-  <si>
-    <t>13,569,355.0</t>
-  </si>
-  <si>
-    <t>6,146,440.0</t>
-  </si>
-  <si>
-    <t>NIBPO</t>
-  </si>
-  <si>
-    <t>2,676,215.5</t>
-  </si>
-  <si>
-    <t>RMDC</t>
-  </si>
-  <si>
-    <t>2,583,672.0</t>
-  </si>
-  <si>
-    <t>5,715,810.0</t>
-  </si>
-  <si>
-    <t>5,683,545.6</t>
-  </si>
-  <si>
-    <t>OHL</t>
-  </si>
-  <si>
-    <t>4,354,191.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>3,043,692.0</t>
-  </si>
-  <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>2,820,182.6</t>
-  </si>
-  <si>
-    <t>42,173,009.0</t>
-  </si>
-  <si>
-    <t>MEGA</t>
-  </si>
-  <si>
-    <t>11,065,321.2</t>
-  </si>
-  <si>
-    <t>2,728,556.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>1,846,544.8</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>1,645,087.4</t>
-  </si>
-  <si>
-    <t>10,475,753.19</t>
-  </si>
-  <si>
-    <t>10,257,349.0</t>
-  </si>
-  <si>
-    <t>3,872,099.5</t>
-  </si>
-  <si>
-    <t>3,158,288.0</t>
-  </si>
-  <si>
-    <t>2,195,150.0</t>
-  </si>
-  <si>
-    <t>4,856,843.59</t>
-  </si>
-  <si>
-    <t>3,350,782.7</t>
-  </si>
-  <si>
-    <t>2,490,580.0</t>
-  </si>
-  <si>
-    <t>CIT</t>
-  </si>
-  <si>
-    <t>1,247,885.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>1,005,454.9</t>
-  </si>
-  <si>
-    <t>6,683,342.2</t>
-  </si>
-  <si>
-    <t>JBBL</t>
-  </si>
-  <si>
-    <t>1,720,200.0</t>
-  </si>
-  <si>
-    <t>1,602,060.0</t>
-  </si>
-  <si>
-    <t>1,240,282.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>630,491.1</t>
+    <t>2,531,130.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -506,103 +503,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>80,766,720.8</t>
-  </si>
-  <si>
-    <t>62,738,097.9</t>
-  </si>
-  <si>
-    <t>54,131,519.9</t>
-  </si>
-  <si>
-    <t>49,473,823.7</t>
-  </si>
-  <si>
-    <t>36,097,659.9</t>
+    <t>81,234,799.8</t>
+  </si>
+  <si>
+    <t>55,008,029.9</t>
+  </si>
+  <si>
+    <t>50,207,274.4</t>
+  </si>
+  <si>
+    <t>48,195,521.1</t>
+  </si>
+  <si>
+    <t>35,345,246.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>228,522,891.0</t>
+    <t>214,084,760.6</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>221,143,077.9</t>
+    <t>206,058,400.8</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>147,580,331.1</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>139,795,100.69</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>126,112,532.8</t>
+    <t>138,374,497.69</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>58,056,836.8</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>51,064,044.3</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>48,306,337.8</t>
+    <t>46,113,722.5</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>42,939,492.29</t>
+    <t>40,794,370.7</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>28,997,087.4</t>
+    <t>32,020,522.9</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>28,953,050.1</t>
+    <t>30,693,523.9</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>25,849,092.0</t>
+    <t>23,260,018.3</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>11,783,914.5</t>
+    <t>11,187,412.5</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>8,818,566.0</t>
+    <t>10,064,486.6</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>3,274,155.0</t>
+    <t>4,953,265.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>2,163,168.34</t>
+    <t>1,968,749.74</t>
   </si>
   <si>
     <t>Total</t>
@@ -614,205 +611,211 @@
     <t>100%</t>
   </si>
   <si>
-    <t>25,946,639.5</t>
-  </si>
-  <si>
-    <t>13,762,876.0</t>
-  </si>
-  <si>
-    <t>10,860,176.4</t>
-  </si>
-  <si>
-    <t>8,501,595.3</t>
-  </si>
-  <si>
-    <t>6,527,133.0</t>
-  </si>
-  <si>
-    <t>10,402,515.5</t>
-  </si>
-  <si>
-    <t>7,476,019.8</t>
-  </si>
-  <si>
-    <t>5,130,644.8</t>
-  </si>
-  <si>
-    <t>3,464,674.0</t>
-  </si>
-  <si>
-    <t>2,959,372.4</t>
-  </si>
-  <si>
-    <t>10,414,835.1</t>
-  </si>
-  <si>
-    <t>9,754,734.5</t>
-  </si>
-  <si>
-    <t>9,462,035.4</t>
-  </si>
-  <si>
-    <t>6,791,976.0</t>
-  </si>
-  <si>
-    <t>4,407,760.0</t>
-  </si>
-  <si>
-    <t>7,268,640.4</t>
-  </si>
-  <si>
-    <t>6,352,080.5</t>
-  </si>
-  <si>
-    <t>3,592,335.3</t>
-  </si>
-  <si>
-    <t>1,401,502.0</t>
-  </si>
-  <si>
-    <t>4,904,359.0</t>
-  </si>
-  <si>
-    <t>3,946,475.5</t>
-  </si>
-  <si>
-    <t>3,575,741.3</t>
-  </si>
-  <si>
-    <t>3,015,029.6</t>
-  </si>
-  <si>
-    <t>1,719,306.0</t>
-  </si>
-  <si>
-    <t>9,881,593.19</t>
-  </si>
-  <si>
-    <t>7,128,196.0</t>
-  </si>
-  <si>
-    <t>5,033,897.3</t>
-  </si>
-  <si>
-    <t>4,288,748.09</t>
-  </si>
-  <si>
-    <t>3,208,327.6</t>
-  </si>
-  <si>
-    <t>10,102,771.0</t>
-  </si>
-  <si>
-    <t>9,791,134.3</t>
-  </si>
-  <si>
-    <t>3,326,628.3</t>
-  </si>
-  <si>
-    <t>3,294,556.1</t>
-  </si>
-  <si>
-    <t>22,986,382.1</t>
-  </si>
-  <si>
-    <t>16,545,318.1</t>
-  </si>
-  <si>
-    <t>10,655,455.8</t>
-  </si>
-  <si>
-    <t>9,257,416.5</t>
+    <t>19,586,760.1</t>
+  </si>
+  <si>
+    <t>17,544,278.7</t>
+  </si>
+  <si>
+    <t>11,841,986.6</t>
+  </si>
+  <si>
+    <t>7,664,721.0</t>
+  </si>
+  <si>
+    <t>5,893,041.3</t>
+  </si>
+  <si>
+    <t>9,648,378.6</t>
+  </si>
+  <si>
+    <t>6,159,450.8</t>
+  </si>
+  <si>
+    <t>5,727,597.5</t>
+  </si>
+  <si>
+    <t>3,067,126.5</t>
+  </si>
+  <si>
+    <t>2,375,131.0</t>
+  </si>
+  <si>
+    <t>9,018,893.4</t>
+  </si>
+  <si>
+    <t>7,792,876.0</t>
+  </si>
+  <si>
+    <t>7,489,775.4</t>
+  </si>
+  <si>
+    <t>6,821,861.2</t>
+  </si>
+  <si>
+    <t>5,004,488.8</t>
+  </si>
+  <si>
+    <t>6,494,780.5</t>
+  </si>
+  <si>
+    <t>6,070,852.4</t>
+  </si>
+  <si>
+    <t>3,457,011.3</t>
+  </si>
+  <si>
+    <t>1,918,016.0</t>
+  </si>
+  <si>
+    <t>9,852,540.0</t>
+  </si>
+  <si>
+    <t>9,553,013.6</t>
+  </si>
+  <si>
+    <t>5,901,617.2</t>
+  </si>
+  <si>
+    <t>3,508,613.0</t>
+  </si>
+  <si>
+    <t>3,488,436.1</t>
+  </si>
+  <si>
+    <t>9,146,586.69</t>
+  </si>
+  <si>
+    <t>8,717,038.4</t>
+  </si>
+  <si>
+    <t>4,749,751.59</t>
+  </si>
+  <si>
+    <t>4,602,835.3</t>
+  </si>
+  <si>
+    <t>1,721,692.0</t>
+  </si>
+  <si>
+    <t>4,881,072.0</t>
+  </si>
+  <si>
+    <t>4,798,833.5</t>
+  </si>
+  <si>
+    <t>3,825,885.3</t>
+  </si>
+  <si>
+    <t>2,658,107.2</t>
+  </si>
+  <si>
+    <t>1,989,384.0</t>
+  </si>
+  <si>
+    <t>17,946,305.1</t>
+  </si>
+  <si>
+    <t>17,037,406.0</t>
+  </si>
+  <si>
+    <t>15,926,680.0</t>
+  </si>
+  <si>
+    <t>10,879,542.5</t>
   </si>
   <si>
     <t>3,572,939.2</t>
   </si>
   <si>
-    <t>28,283,541.2</t>
-  </si>
-  <si>
-    <t>17,886,436.2</t>
-  </si>
-  <si>
-    <t>8,636,190.69</t>
-  </si>
-  <si>
-    <t>6,296,157.5</t>
-  </si>
-  <si>
-    <t>3,558,769.5</t>
-  </si>
-  <si>
-    <t>13,863,880.3</t>
-  </si>
-  <si>
-    <t>12,420,942.4</t>
-  </si>
-  <si>
-    <t>6,988,760.0</t>
-  </si>
-  <si>
-    <t>6,325,431.6</t>
+    <t>29,302,814.1</t>
+  </si>
+  <si>
+    <t>14,136,128.2</t>
+  </si>
+  <si>
+    <t>7,875,446.7</t>
+  </si>
+  <si>
+    <t>6,760,112.5</t>
+  </si>
+  <si>
+    <t>3,819,169.5</t>
+  </si>
+  <si>
+    <t>12,399,012.9</t>
+  </si>
+  <si>
+    <t>11,661,784.4</t>
+  </si>
+  <si>
+    <t>8,116,439.8</t>
   </si>
   <si>
     <t>5,680,800.5</t>
   </si>
   <si>
-    <t>13,914,073.5</t>
+    <t>5,490,979.1</t>
+  </si>
+  <si>
+    <t>45,743,522.0</t>
+  </si>
+  <si>
+    <t>9,895,101.4</t>
   </si>
   <si>
     <t>3,035,928.6</t>
   </si>
   <si>
-    <t>2,163,376.4</t>
-  </si>
-  <si>
-    <t>1,941,424.6</t>
-  </si>
-  <si>
-    <t>17,479,067.39</t>
-  </si>
-  <si>
-    <t>13,041,306.3</t>
-  </si>
-  <si>
-    <t>5,393,989.0</t>
-  </si>
-  <si>
-    <t>4,410,851.0</t>
-  </si>
-  <si>
-    <t>3,297,974.0</t>
-  </si>
-  <si>
-    <t>8,431,082.4</t>
-  </si>
-  <si>
-    <t>6,979,305.9</t>
-  </si>
-  <si>
-    <t>5,769,928.6</t>
-  </si>
-  <si>
-    <t>2,897,921.0</t>
-  </si>
-  <si>
-    <t>1,684,685.9</t>
-  </si>
-  <si>
-    <t>10,701,404.9</t>
-  </si>
-  <si>
-    <t>3,420,927.1</t>
-  </si>
-  <si>
-    <t>2,924,645.3</t>
-  </si>
-  <si>
-    <t>2,187,015.0</t>
+    <t>2,298,840.0</t>
+  </si>
+  <si>
+    <t>1,634,145.6</t>
+  </si>
+  <si>
+    <t>13,563,135.1</t>
+  </si>
+  <si>
+    <t>3,332,308.1</t>
+  </si>
+  <si>
+    <t>2,724,165.3</t>
   </si>
   <si>
     <t>702,619.5</t>
+  </si>
+  <si>
+    <t>687,151.0</t>
+  </si>
+  <si>
+    <t>9,347,751.6</t>
+  </si>
+  <si>
+    <t>7,797,901.5</t>
+  </si>
+  <si>
+    <t>6,626,502.9</t>
+  </si>
+  <si>
+    <t>1,772,087.0</t>
+  </si>
+  <si>
+    <t>1,056,657.0</t>
+  </si>
+  <si>
+    <t>14,227,715.6</t>
+  </si>
+  <si>
+    <t>7,381,873.4</t>
+  </si>
+  <si>
+    <t>6,018,894.0</t>
+  </si>
+  <si>
+    <t>5,748,084.0</t>
+  </si>
+  <si>
+    <t>2,264,634.0</t>
   </si>
 </sst>
 </file>
@@ -1641,61 +1644,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1254455027881266</v>
+        <v>0.08580646470367577</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.05807081358371965</v>
+        <v>0.03378957252903035</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04996256473307926</v>
+        <v>0.04687941771264783</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.03468482634339091</v>
+        <v>0.03939047119824442</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.04300605925826948</v>
+        <v>0.1091538160280437</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.06586835719027148</v>
+        <v>0.04151256613122681</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1304311490989191</v>
+        <v>0.05488097796722088</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1707,61 +1710,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03467283417001304</v>
+        <v>0.03005916521637354</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03506221821139935</v>
+        <v>0.02896491536024869</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03849607386678166</v>
+        <v>0.04488695383136188</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02672635365336287</v>
+        <v>0.02600012814082861</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02624406344122884</v>
+        <v>0.06818063409652354</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03544034977382983</v>
+        <v>0.0343603016446075</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V10" s="18">
-        <v>0.073787046269347</v>
+        <v>0.03287839858610713</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1773,61 +1776,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02957507490216257</v>
+        <v>0.02913509287226105</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03072178552843126</v>
+        <v>0.02214438396960767</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.03134415705614529</v>
+        <v>0.03512669783689052</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02269981278653119</v>
+        <v>0.02320444357701074</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02622346267274796</v>
+        <v>0.04869877132901516</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03301388255121318</v>
+        <v>0.03396788480395133</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="U11" s="17" t="s">
         <v>105</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04633305918440658</v>
+        <v>0.0219139260767654</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1839,61 +1842,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02328110542149111</v>
+        <v>0.02287001101019181</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.01736877078203668</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.02298725429245163</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.01749883509918228</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.04264999474250289</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="12">
-        <v>0.01643535246813515</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.03029846617833371</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0.01771385975240943</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0.02510950512535262</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>98</v>
-      </c>
       <c r="R12" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S12" s="16">
-        <v>0.0309291425647352</v>
+        <v>0.0315287344610404</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>106</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04289100048126342</v>
+        <v>0.02078844489191107</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1905,61 +1908,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02133607863592987</v>
+        <v>0.02073531340294325</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01638062611218128</v>
+        <v>0.01691137739910454</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01939182982962546</v>
+        <v>0.01978039937845075</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01618512186166925</v>
+        <v>0.01472853394174001</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01597498265712858</v>
+        <v>0.04212364064795</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02863438130315876</v>
+        <v>0.02455623170920389</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02535435766831396</v>
+        <v>0.01121510652851788</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1970,7 +1973,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1979,7 +1982,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1988,7 +1991,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1997,7 +2000,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2006,7 +2009,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2015,7 +2018,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2024,7 +2027,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2033,49 +2036,49 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" s="10">
-        <v>0.09872842957414189</v>
+        <v>0.1008936313939632</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1516893838563957</v>
+        <v>0.1308732822358734</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J16" s="14">
-        <v>0.05343594160464366</v>
+        <v>0.05854187398297863</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M16" s="16">
-        <v>0.4788761325404492</v>
+        <v>0.5088485361115058</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1478748570207291</v>
+        <v>0.1427910421398674</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>54</v>
@@ -2084,196 +2087,196 @@
         <v>144</v>
       </c>
       <c r="S16" s="16">
-        <v>0.07651068750568374</v>
+        <v>0.07495729716901302</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="U16" s="17" t="s">
         <v>151</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1107969292346761</v>
+        <v>0.1009593801206678</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04956846863222417</v>
+        <v>0.04967335496113059</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" s="12">
-        <v>0.126153291734371</v>
+        <v>0.1175769392938133</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>0.0531343083113206</v>
+        <v>0.04430347398047561</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1256471460590787</v>
+        <v>0.07761403706478066</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1447918815791421</v>
+        <v>0.0241461406507903</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="R17" s="15" t="s">
         <v>145</v>
       </c>
       <c r="S17" s="16">
-        <v>0.05278545268765732</v>
+        <v>0.0330219720229838</v>
       </c>
       <c r="T17" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="U17" s="17" t="s">
-        <v>153</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.02851759972270906</v>
+        <v>0.06907383932323938</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="D18" s="10">
-        <v>0.04212608324619932</v>
+        <v>0.02920555165304127</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>54</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05714299894488775</v>
+        <v>0.05888195435510342</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04070644335824056</v>
+        <v>0.03621228679904309</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03098285789140722</v>
+        <v>0.03060676378390027</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05465823306457208</v>
+        <v>0.01869344694870573</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="R18" s="15" t="s">
         <v>146</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03923453250335378</v>
+        <v>0.02036212851998611</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02655906627820212</v>
+        <v>0.05317732797875354</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02443889611829368</v>
+        <v>0.02548835195012443</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0248805779431333</v>
+        <v>0.0293316068418293</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0284548555628198</v>
+        <v>0.02869508628337389</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02096758693188521</v>
+        <v>0.02071306599900804</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04458212956279694</v>
+        <v>0.008820190023799725</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>147</v>
@@ -2282,16 +2285,16 @@
         <v>148</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01965814573029079</v>
+        <v>0.0201414076950211</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02056148448975761</v>
+        <v>0.04898903527076721</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2300,46 +2303,46 @@
         <v>54</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0223070850128679</v>
+        <v>0.02429213190254347</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02402020785526842</v>
+        <v>0.02911893113958313</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02636531178048818</v>
+        <v>0.02363522268279065</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01868003043849735</v>
+        <v>0.01845327765150162</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>143</v>
       </c>
       <c r="P20" s="18">
-        <v>0.03098655401590156</v>
+        <v>0.008456333972657491</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>149</v>
@@ -2348,240 +2351,240 @@
         <v>150</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01583910292169147</v>
+        <v>0.01798709180154962</v>
       </c>
       <c r="T20" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="U20" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01045232694950037</v>
+        <v>0.03923915612829204</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>158</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>161</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="D31" s="22">
-        <v>0.236759542607334</v>
+        <v>0.2218010186071758</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>171</v>
-      </c>
       <c r="D32" s="22">
-        <v>0.2291137388699587</v>
+        <v>0.2134853646841301</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D33" s="22">
-        <v>0.1448337361550279</v>
+        <v>0.1528995696500046</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>175</v>
-      </c>
       <c r="D34" s="22">
-        <v>0.1306580073975189</v>
+        <v>0.1433619303545901</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>177</v>
-      </c>
       <c r="D35" s="22">
-        <v>0.05290454588266451</v>
+        <v>0.06014937963478082</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>179</v>
-      </c>
       <c r="D36" s="22">
-        <v>0.05004744335465006</v>
+        <v>0.04777579961134627</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>181</v>
-      </c>
       <c r="D37" s="22">
-        <v>0.04448716061770434</v>
+        <v>0.04226472239004726</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>183</v>
-      </c>
       <c r="D38" s="22">
-        <v>0.03004222955401386</v>
+        <v>0.03317463875359281</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>185</v>
-      </c>
       <c r="D39" s="22">
-        <v>0.0299966050174082</v>
+        <v>0.03179981072255591</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>187</v>
-      </c>
       <c r="D40" s="22">
-        <v>0.02678077094138852</v>
+        <v>0.02409837924615709</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C41" s="21" t="s">
-        <v>189</v>
-      </c>
       <c r="D41" s="22">
-        <v>0.01220864218431374</v>
+        <v>0.01159064045999476</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>191</v>
-      </c>
       <c r="D42" s="22">
-        <v>0.009136413614741934</v>
+        <v>0.01042724093663616</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C43" s="21" t="s">
-        <v>193</v>
-      </c>
       <c r="D43" s="22">
-        <v>0.003392165383666163</v>
+        <v>0.005131795553089324</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="21" t="s">
-        <v>195</v>
-      </c>
       <c r="D44" s="22">
-        <v>0.002241135426389586</v>
+        <v>0.002039709395899021</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="D45" s="20" t="s">
         <v>197</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2960,331 +2963,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1709376908781737</v>
+        <v>0.1298024112190303</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G9" s="12">
-        <v>0.09671141868149342</v>
+        <v>0.09229829499334005</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J9" s="14">
-        <v>0.09736616861400101</v>
+        <v>0.09176637154400971</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M9" s="16">
-        <v>0.08253569015147257</v>
+        <v>0.07285326472749018</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P9" s="18">
-        <v>0.06922952193101745</v>
+        <v>0.14849682072303</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1556664269328107</v>
+        <v>0.1406554794461111</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1674844666132968</v>
+        <v>0.07566942285913196</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09067047943848897</v>
+        <v>0.1162667877041428</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G10" s="12">
-        <v>0.06950400419484448</v>
+        <v>0.05892252268535196</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J10" s="14">
-        <v>0.09119502277206605</v>
+        <v>0.07929176260275969</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M10" s="16">
-        <v>0.07212811738013768</v>
+        <v>0.06809797760197117</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P10" s="18">
-        <v>0.0557081184671581</v>
+        <v>0.1439823789524191</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1122916901493935</v>
+        <v>0.1340499200102877</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1623181309142467</v>
+        <v>0.07439451033339976</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D11" s="10">
-        <v>0.07154735688780187</v>
+        <v>0.07847742079117241</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0476992259573011</v>
+        <v>0.05479132873767174</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J11" s="14">
-        <v>0.08845863859986093</v>
+        <v>0.07620774319580981</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04079110492809594</v>
+        <v>0.03939047119824442</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05047486547130722</v>
+        <v>0.08894877781002163</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07929984470902153</v>
+        <v>0.07304130059226721</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>103</v>
+        <v>229</v>
       </c>
       <c r="V11" s="18">
-        <v>0.073787046269347</v>
+        <v>0.05931126043136362</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05600891280594292</v>
+        <v>0.05079447861931678</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03221081841299679</v>
+        <v>0.02934073777731842</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06349679798946102</v>
+        <v>0.06941178055179852</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03468482634339091</v>
+        <v>0.03877799402224986</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04255990595628639</v>
+        <v>0.05288157933360256</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S12" s="16">
-        <v>0.06756138197855389</v>
+        <v>0.07078203346970785</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>230</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05514908399351013</v>
+        <v>0.04120763588853089</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D13" s="10">
-        <v>0.04300106158544063</v>
+        <v>0.03905347113294805</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02751306673956468</v>
+        <v>0.0227209721730682</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J13" s="14">
-        <v>0.04120724901060115</v>
+        <v>0.05092019145149618</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01591410889148803</v>
+        <v>0.02151477288563667</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02426957986418406</v>
+        <v>0.05257747445282598</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S13" s="16">
-        <v>0.05054133314473217</v>
+        <v>0.02647604201013411</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>231</v>
       </c>
       <c r="V13" s="18">
-        <v>0.05461738874770925</v>
+        <v>0.03084067170596774</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3295,7 +3298,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3304,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3313,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3322,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3331,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3340,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3349,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3358,331 +3361,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>232</v>
       </c>
       <c r="D16" s="10">
-        <v>0.151435374812888</v>
+        <v>0.1189310361978845</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>237</v>
       </c>
       <c r="G16" s="12">
-        <v>0.262949994622788</v>
+        <v>0.2803165062300524</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>242</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1296105885473047</v>
+        <v>0.1261587618454798</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>131</v>
+        <v>247</v>
       </c>
       <c r="M16" s="16">
-        <v>0.4788761325404492</v>
+        <v>0.5131143258550109</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2467330552070172</v>
+        <v>0.2044226606932766</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="S16" s="16">
-        <v>0.132816282336345</v>
+        <v>0.1437489772049231</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1774086626025098</v>
+        <v>0.220566922195753</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1090013398790565</v>
+        <v>0.1129077176841296</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>238</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1662888769603872</v>
+        <v>0.1352289938816531</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>243</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1161208564947125</v>
+        <v>0.1186575328760995</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M17" s="16">
-        <v>0.157994837540844</v>
+        <v>0.1109953510822358</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1840899902525419</v>
+        <v>0.05022432372967792</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1099461989514084</v>
+        <v>0.1199155062025541</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V17" s="18">
-        <v>0.05671237630413203</v>
+        <v>0.1144384061118496</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>234</v>
       </c>
       <c r="D18" s="10">
-        <v>0.07019864787139171</v>
+        <v>0.105546882494053</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>239</v>
       </c>
       <c r="G18" s="12">
-        <v>0.08029002740740158</v>
+        <v>0.0753380783296508</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>244</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06533649145945533</v>
+        <v>0.08258399309846459</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03447308553764661</v>
+        <v>0.03405462432326368</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07614109810704454</v>
+        <v>0.04105843631936529</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S18" s="16">
-        <v>0.0908946716020889</v>
+        <v>0.1019018321283223</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04848498081403463</v>
+        <v>0.09330864925374839</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>235</v>
       </c>
       <c r="D19" s="10">
-        <v>0.06098829869692777</v>
+        <v>0.072099256959803</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>240</v>
       </c>
       <c r="G19" s="12">
-        <v>0.05853491149012226</v>
+        <v>0.06466857112273408</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>245</v>
       </c>
       <c r="J19" s="14">
-        <v>0.05913516957382552</v>
+        <v>0.05780159784906606</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02456522188543103</v>
+        <v>0.0257865526150027</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0622632042309607</v>
+        <v>0.0105898338832428</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04565144491108557</v>
+        <v>0.02725101229349531</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03625649247620077</v>
+        <v>0.08911038370788439</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>236</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02353869280436525</v>
+        <v>0.02367804174509663</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>241</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0330856173302918</v>
+        <v>0.0365349296244</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>246</v>
       </c>
       <c r="J20" s="14">
-        <v>0.05310864493144987</v>
+        <v>0.05587018338979281</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02204495069504973</v>
+        <v>0.01833054127080404</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04655392546934784</v>
+        <v>0.01035669369083006</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02653914497887714</v>
+        <v>0.01624918691746392</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01164807676919543</v>
+        <v>0.03510776890141498</v>
       </c>
     </row>
   </sheetData>
